--- a/3DAG and 2D Tree/Data Summaries/CRAWDAD 1 - 10,000.xlsx
+++ b/3DAG and 2D Tree/Data Summaries/CRAWDAD 1 - 10,000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cvinc\Desktop\College\Internship\Github\Multi-Dimensional-Data-Structure\3DAG and 2D Tree\Data Summaries\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{301AF885-2400-441D-BB87-F20AE3B66646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99D06CD0-EA32-498E-A12D-A2F1467B359C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" xr2:uid="{350691A1-EBA1-4BDB-A934-ABFC69ADBA66}"/>
   </bookViews>
@@ -2769,28 +2769,28 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>-174.2961</c:v>
+                  <c:v>1.0118</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>-213.35890000000001</c:v>
+                  <c:v>1.0089999999999999</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>-250.77440000000001</c:v>
+                  <c:v>0.99199999999999999</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>-276.66770000000002</c:v>
+                  <c:v>0.91500000000000004</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>-304.87720000000002</c:v>
+                  <c:v>0.86150000000000004</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>-334.1354</c:v>
+                  <c:v>0.81469999999999998</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>-363.87</c:v>
+                  <c:v>0.79149999999999998</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>-391.7353</c:v>
+                  <c:v>0.76070000000000004</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -16181,7 +16181,7 @@
         <v>8.0186540900000001</v>
       </c>
       <c r="D145" s="2">
-        <v>-174.2961</v>
+        <v>1.0118</v>
       </c>
     </row>
     <row r="146" spans="2:15" x14ac:dyDescent="0.45">
@@ -16192,7 +16192,7 @@
         <v>6.7772911899999997</v>
       </c>
       <c r="D146" s="2">
-        <v>-213.35890000000001</v>
+        <v>1.0089999999999999</v>
       </c>
     </row>
     <row r="147" spans="2:15" x14ac:dyDescent="0.45">
@@ -16203,7 +16203,7 @@
         <v>5.6469419199999997</v>
       </c>
       <c r="D147" s="2">
-        <v>-250.77440000000001</v>
+        <v>0.99199999999999999</v>
       </c>
     </row>
     <row r="148" spans="2:15" x14ac:dyDescent="0.45">
@@ -16214,7 +16214,7 @@
         <v>4.9350163699999996</v>
       </c>
       <c r="D148" s="2">
-        <v>-276.66770000000002</v>
+        <v>0.91500000000000004</v>
       </c>
     </row>
     <row r="149" spans="2:15" x14ac:dyDescent="0.45">
@@ -16225,7 +16225,7 @@
         <v>4.3145914799999998</v>
       </c>
       <c r="D149" s="2">
-        <v>-304.87720000000002</v>
+        <v>0.86150000000000004</v>
       </c>
     </row>
     <row r="150" spans="2:15" x14ac:dyDescent="0.45">
@@ -16236,7 +16236,7 @@
         <v>3.6445403399999998</v>
       </c>
       <c r="D150" s="2">
-        <v>-334.1354</v>
+        <v>0.81469999999999998</v>
       </c>
     </row>
     <row r="151" spans="2:15" x14ac:dyDescent="0.45">
@@ -16247,7 +16247,7 @@
         <v>3.1000146700000002</v>
       </c>
       <c r="D151" s="2">
-        <v>-363.87</v>
+        <v>0.79149999999999998</v>
       </c>
     </row>
     <row r="152" spans="2:15" x14ac:dyDescent="0.45">
@@ -16258,7 +16258,7 @@
         <v>2.68888558</v>
       </c>
       <c r="D152" s="2">
-        <v>-391.7353</v>
+        <v>0.76070000000000004</v>
       </c>
     </row>
     <row r="157" spans="2:15" x14ac:dyDescent="0.45">
